--- a/data/trans_dic/P32E$amigos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,1</t>
+          <t>0,0; 69,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,24</t>
+          <t>0,0; 65,27</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 40,24</t>
+          <t>4,75; 42,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 41,77</t>
+          <t>4,56; 42,04</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,57</t>
+          <t>0,0; 85,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,89</t>
+          <t>0,0; 60,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 67,17</t>
+          <t>11,51; 68,49</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,5; 46,13</t>
+          <t>11,09; 47,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,22</t>
+          <t>0,0; 67,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,4; 44,18</t>
+          <t>11,92; 43,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,28; 40,25</t>
+          <t>11,72; 39,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 57,99</t>
+          <t>5,28; 53,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 38,44</t>
+          <t>13,71; 39,87</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,22; 35,91</t>
+          <t>9,59; 35,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 44,31</t>
+          <t>6,33; 44,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 32,45</t>
+          <t>10,62; 32,36</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,21; 33,2</t>
+          <t>15,84; 32,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,36; 36,29</t>
+          <t>9,91; 34,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,61</t>
+          <t>16,39; 29,47</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1256</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1289</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7040</t>
+          <t>0; 7041</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8239</t>
+          <t>0; 7880</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>700; 6035</t>
+          <t>713; 6375</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>716; 6678</t>
+          <t>728; 6722</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9529</t>
+          <t>0; 9388</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6794</t>
+          <t>0; 6279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2269; 14319</t>
+          <t>2453; 14601</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1135</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 310</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 948</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2882; 12665</t>
+          <t>3045; 12902</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4805</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4279; 15241</t>
+          <t>4112; 14950</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4047; 13263</t>
+          <t>3863; 13119</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>831; 8868</t>
+          <t>807; 8174</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6077; 18548</t>
+          <t>6614; 19233</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3462; 15126</t>
+          <t>4039; 14883</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1026; 7061</t>
+          <t>1009; 7104</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5916; 18842</t>
+          <t>6165; 18785</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>23355; 47840</t>
+          <t>22821; 46973</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6761; 19857</t>
+          <t>5425; 18865</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33115; 60859</t>
+          <t>32587; 58588</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$amigos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Provincia-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,11</t>
+          <t>0,0; 68,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,27</t>
+          <t>0,0; 61,55</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 42,5</t>
+          <t>4,78; 39,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 42,04</t>
+          <t>4,47; 36,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,29</t>
+          <t>0,0; 89,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,9</t>
+          <t>0,0; 65,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 68,49</t>
+          <t>11,65; 71,66</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 47,0</t>
+          <t>8,7; 44,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,06</t>
+          <t>0,0; 66,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,92; 43,34</t>
+          <t>10,92; 38,66</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,72; 39,81</t>
+          <t>12,13; 44,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 53,46</t>
+          <t>9,46; 57,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 39,87</t>
+          <t>15,04; 43,02</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,59; 35,33</t>
+          <t>9,54; 35,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 44,58</t>
+          <t>6,96; 45,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 32,36</t>
+          <t>10,36; 31,97</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,84; 32,6</t>
+          <t>16,03; 33,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,91; 34,48</t>
+          <t>12,97; 36,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,39; 29,47</t>
+          <t>17,31; 31,07</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3013</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7041</t>
+          <t>0; 6848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>0; 1804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7880</t>
+          <t>0; 7261</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2551</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>713; 6375</t>
+          <t>776; 6432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>728; 6722</t>
+          <t>767; 6293</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>9366</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9388</t>
+          <t>0; 10653</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6279</t>
+          <t>0; 7562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2453; 14601</t>
+          <t>2728; 16786</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8147</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3045; 12902</t>
+          <t>2373; 12228</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4112; 14950</t>
+          <t>3759; 13309</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>17284</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3863; 13119</t>
+          <t>5325; 19636</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>807; 8174</t>
+          <t>1858; 11358</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6614; 19233</t>
+          <t>9561; 27344</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12567</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4039; 14883</t>
+          <t>4463; 16560</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1009; 7104</t>
+          <t>1286; 8357</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6165; 18785</t>
+          <t>6758; 20859</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>22821; 46973</t>
+          <t>25878; 53549</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5425; 18865</t>
+          <t>8327; 23332</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32587; 58588</t>
+          <t>39074; 70110</t>
         </is>
       </c>
     </row>
